--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>125685411</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>125685366</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>125685411</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>125685366</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>125685411</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>125685366</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>125685463</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>62515025</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493202.0872900187</v>
+        <v>493202</v>
       </c>
       <c r="R2" t="n">
-        <v>7093983.839080138</v>
+        <v>7093984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125685411</v>
+        <v>125684959</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493116</v>
+        <v>493277</v>
       </c>
       <c r="R3" t="n">
-        <v>7093925</v>
+        <v>7093987</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av gran.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125685366</v>
+        <v>125684993</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493133</v>
+        <v>493273</v>
       </c>
       <c r="R4" t="n">
-        <v>7093926</v>
+        <v>7093990</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -998,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack vid basen. Äldre längre upp på gran.</t>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125685463</v>
+        <v>125685143</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,37 +1036,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493103</v>
+        <v>493264</v>
       </c>
       <c r="R5" t="n">
-        <v>7093936</v>
+        <v>7093951</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på basen gran bredvid  bäcken med stor granlåga bredvid.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1124,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,6 +1139,240 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125685366</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493133</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093926</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack vid basen. Äldre längre upp på gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125685411</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493116</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093925</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på basen av gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57468-2024 artfynd.xlsx
+++ b/artfynd/A 57468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Myrskyddsplaneinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62515025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685366</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,8 +1403,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685411</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>